--- a/data/analysis_pixtral_12b_panns/summary.xlsx
+++ b/data/analysis_pixtral_12b_panns/summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>combo</t>
   </si>
@@ -49,7 +49,28 @@
     <t>pixtral_12b_panns</t>
   </si>
   <si>
-    <t>panns_w2.5s_h1.25s</t>
+    <t>panns_w1_0s_h1_0s</t>
+  </si>
+  <si>
+    <t>panns_w1_0s_h0_5s</t>
+  </si>
+  <si>
+    <t>panns_w2_5s_h2_5s</t>
+  </si>
+  <si>
+    <t>panns_w2_5s_h1_25s</t>
+  </si>
+  <si>
+    <t>panns_w5_0s_h5_0s</t>
+  </si>
+  <si>
+    <t>panns_w5_0s_h2_5s</t>
+  </si>
+  <si>
+    <t>panns_w10_0s_h10_0s</t>
+  </si>
+  <si>
+    <t>panns_w10_0s_h5_0s</t>
   </si>
   <si>
     <t>pixtral_12b</t>
@@ -410,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -453,27 +474,251 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>0.76</v>
+      </c>
+      <c r="E2">
+        <v>0.633</v>
+      </c>
+      <c r="F2">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G2">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>0.75</v>
-      </c>
-      <c r="E2">
-        <v>0.7</v>
-      </c>
-      <c r="F2">
-        <v>0.724</v>
-      </c>
-      <c r="G2">
-        <v>21</v>
-      </c>
-      <c r="H2">
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>0.76</v>
+      </c>
+      <c r="E3">
+        <v>0.633</v>
+      </c>
+      <c r="F3">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G3">
+        <v>19</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>0.731</v>
+      </c>
+      <c r="E4">
+        <v>0.633</v>
+      </c>
+      <c r="F4">
+        <v>0.679</v>
+      </c>
+      <c r="G4">
+        <v>19</v>
+      </c>
+      <c r="H4">
         <v>7</v>
       </c>
-      <c r="I2">
-        <v>9</v>
-      </c>
-      <c r="J2">
+      <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>0.731</v>
+      </c>
+      <c r="E5">
+        <v>0.633</v>
+      </c>
+      <c r="F5">
+        <v>0.679</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>0.792</v>
+      </c>
+      <c r="E6">
+        <v>0.633</v>
+      </c>
+      <c r="F6">
+        <v>0.704</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>0.731</v>
+      </c>
+      <c r="E7">
+        <v>0.633</v>
+      </c>
+      <c r="F7">
+        <v>0.679</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>0.792</v>
+      </c>
+      <c r="E8">
+        <v>0.633</v>
+      </c>
+      <c r="F8">
+        <v>0.704</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>11</v>
+      </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>0.792</v>
+      </c>
+      <c r="E9">
+        <v>0.633</v>
+      </c>
+      <c r="F9">
+        <v>0.704</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
         <v>30</v>
       </c>
     </row>

--- a/data/analysis_pixtral_12b_panns/summary.xlsx
+++ b/data/analysis_pixtral_12b_panns/summary.xlsx
@@ -14,15 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
-  <si>
-    <t>combo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+  <si>
+    <t>visual</t>
+  </si>
+  <si>
+    <t>reid</t>
   </si>
   <si>
     <t>audio</t>
   </si>
   <si>
-    <t>visual</t>
+    <t>window</t>
+  </si>
+  <si>
+    <t>hop</t>
   </si>
   <si>
     <t>precision</t>
@@ -46,34 +52,16 @@
     <t>support</t>
   </si>
   <si>
-    <t>pixtral_12b_panns</t>
-  </si>
-  <si>
-    <t>panns_w1_0s_h1_0s</t>
-  </si>
-  <si>
-    <t>panns_w1_0s_h0_5s</t>
-  </si>
-  <si>
-    <t>panns_w2_5s_h2_5s</t>
-  </si>
-  <si>
-    <t>panns_w2_5s_h1_25s</t>
-  </si>
-  <si>
-    <t>panns_w5_0s_h5_0s</t>
-  </si>
-  <si>
-    <t>panns_w5_0s_h2_5s</t>
-  </si>
-  <si>
-    <t>panns_w10_0s_h10_0s</t>
-  </si>
-  <si>
-    <t>panns_w10_0s_h5_0s</t>
+    <t>VPI</t>
+  </si>
+  <si>
+    <t>SPI</t>
   </si>
   <si>
     <t>pixtral_12b</t>
+  </si>
+  <si>
+    <t>panns</t>
   </si>
 </sst>
 </file>
@@ -431,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,261 +453,369 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0.76</v>
+      </c>
+      <c r="G2">
+        <v>0.633</v>
+      </c>
+      <c r="H2">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="I2">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>239</v>
+      </c>
+      <c r="N2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>0.76</v>
+      </c>
+      <c r="G3">
+        <v>0.633</v>
+      </c>
+      <c r="H3">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="I3">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>11</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>239</v>
+      </c>
+      <c r="N3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>2.5</v>
+      </c>
+      <c r="E4">
+        <v>2.5</v>
+      </c>
+      <c r="F4">
+        <v>0.731</v>
+      </c>
+      <c r="G4">
+        <v>0.633</v>
+      </c>
+      <c r="H4">
+        <v>0.679</v>
+      </c>
+      <c r="I4">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4">
+        <v>11</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+      <c r="M4">
+        <v>239</v>
+      </c>
+      <c r="N4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>2.5</v>
+      </c>
+      <c r="E5">
+        <v>1.25</v>
+      </c>
+      <c r="F5">
+        <v>0.731</v>
+      </c>
+      <c r="G5">
+        <v>0.633</v>
+      </c>
+      <c r="H5">
+        <v>0.679</v>
+      </c>
+      <c r="I5">
+        <v>19</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>239</v>
+      </c>
+      <c r="N5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>0.792</v>
+      </c>
+      <c r="G6">
+        <v>0.633</v>
+      </c>
+      <c r="H6">
+        <v>0.704</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>30</v>
+      </c>
+      <c r="M6">
+        <v>239</v>
+      </c>
+      <c r="N6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>2.5</v>
+      </c>
+      <c r="F7">
+        <v>0.731</v>
+      </c>
+      <c r="G7">
+        <v>0.633</v>
+      </c>
+      <c r="H7">
+        <v>0.679</v>
+      </c>
+      <c r="I7">
+        <v>19</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>239</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0.792</v>
+      </c>
+      <c r="G8">
+        <v>0.633</v>
+      </c>
+      <c r="H8">
+        <v>0.704</v>
+      </c>
+      <c r="I8">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="L8">
+        <v>30</v>
+      </c>
+      <c r="M8">
+        <v>239</v>
+      </c>
+      <c r="N8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>0.792</v>
+      </c>
+      <c r="G9">
+        <v>0.633</v>
+      </c>
+      <c r="H9">
+        <v>0.704</v>
+      </c>
+      <c r="I9">
         <v>19</v>
       </c>
-      <c r="D2">
-        <v>0.76</v>
-      </c>
-      <c r="E2">
-        <v>0.633</v>
-      </c>
-      <c r="F2">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="G2">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
         <v>11</v>
       </c>
-      <c r="J2">
+      <c r="L9">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="M9">
+        <v>239</v>
+      </c>
+      <c r="N9">
         <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>0.76</v>
-      </c>
-      <c r="E3">
-        <v>0.633</v>
-      </c>
-      <c r="F3">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="G3">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>0.731</v>
-      </c>
-      <c r="E4">
-        <v>0.633</v>
-      </c>
-      <c r="F4">
-        <v>0.679</v>
-      </c>
-      <c r="G4">
-        <v>19</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
-      </c>
-      <c r="I4">
-        <v>11</v>
-      </c>
-      <c r="J4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>0.731</v>
-      </c>
-      <c r="E5">
-        <v>0.633</v>
-      </c>
-      <c r="F5">
-        <v>0.679</v>
-      </c>
-      <c r="G5">
-        <v>19</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>0.792</v>
-      </c>
-      <c r="E6">
-        <v>0.633</v>
-      </c>
-      <c r="F6">
-        <v>0.704</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
-        <v>0.731</v>
-      </c>
-      <c r="E7">
-        <v>0.633</v>
-      </c>
-      <c r="F7">
-        <v>0.679</v>
-      </c>
-      <c r="G7">
-        <v>19</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>0.792</v>
-      </c>
-      <c r="E8">
-        <v>0.633</v>
-      </c>
-      <c r="F8">
-        <v>0.704</v>
-      </c>
-      <c r="G8">
-        <v>19</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>11</v>
-      </c>
-      <c r="J8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9">
-        <v>0.792</v>
-      </c>
-      <c r="E9">
-        <v>0.633</v>
-      </c>
-      <c r="F9">
-        <v>0.704</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_panns/summary.xlsx
+++ b/data/analysis_pixtral_12b_panns/summary.xlsx
@@ -483,22 +483,22 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.76</v>
+        <v>0.741</v>
       </c>
       <c r="G2">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H2">
-        <v>0.6909999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="I2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L2">
         <v>30</v>
@@ -527,22 +527,22 @@
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>0.76</v>
+        <v>0.741</v>
       </c>
       <c r="G3">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H3">
-        <v>0.6909999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="I3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3">
         <v>30</v>
@@ -571,22 +571,22 @@
         <v>2.5</v>
       </c>
       <c r="F4">
-        <v>0.731</v>
+        <v>0.714</v>
       </c>
       <c r="G4">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H4">
-        <v>0.679</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>30</v>
@@ -615,22 +615,22 @@
         <v>1.25</v>
       </c>
       <c r="F5">
-        <v>0.731</v>
+        <v>0.714</v>
       </c>
       <c r="G5">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H5">
-        <v>0.679</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>30</v>
@@ -659,22 +659,22 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="G6">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H6">
-        <v>0.704</v>
+        <v>0.714</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>30</v>
@@ -703,22 +703,22 @@
         <v>2.5</v>
       </c>
       <c r="F7">
-        <v>0.731</v>
+        <v>0.714</v>
       </c>
       <c r="G7">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H7">
-        <v>0.679</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>30</v>
@@ -747,22 +747,22 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="G8">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H8">
-        <v>0.704</v>
+        <v>0.714</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>30</v>
@@ -791,22 +791,22 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>0.792</v>
+        <v>0.769</v>
       </c>
       <c r="G9">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="H9">
-        <v>0.704</v>
+        <v>0.714</v>
       </c>
       <c r="I9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>30</v>
